--- a/DUC_DCC_LogAPI/Files/reportDCC.xlsx
+++ b/DUC_DCC_LogAPI/Files/reportDCC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\New_Project\DUC_DCC_LogAPI\DUC_DCC_LogAPI\Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\FBNWEB04\wwwroot\custappl\CRUDLogs\dccduc_Api_new\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{532EAD41-BDC6-4B72-B33C-676A71475099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F03624DA-1C4E-4EE9-9EB1-BAFC36C5F5A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{823880ED-C392-4FB6-8B13-B5946B380BBC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{823880ED-C392-4FB6-8B13-B5946B380BBC}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>GROUP NAME</t>
   </si>
@@ -78,10 +78,13 @@
     <t>No.</t>
   </si>
   <si>
-    <t>Is not dcc</t>
-  </si>
-  <si>
     <t xml:space="preserve"> DCC Report Log</t>
+  </si>
+  <si>
+    <t>Is bu dcc</t>
+  </si>
+  <si>
+    <t>POSITION</t>
   </si>
 </sst>
 </file>
@@ -103,22 +106,23 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Cordia New"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Cordia New"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="20"/>
+      <b/>
+      <sz val="18"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Cordia New"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -182,19 +186,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -535,19 +539,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E32F00C-973C-4B55-B3A9-D24B59245FBF}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="18.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="6"/>
-    <col min="2" max="2" width="23.6640625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="22" style="5" customWidth="1"/>
-    <col min="4" max="4" width="18.21875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="26" style="5" customWidth="1"/>
-    <col min="6" max="6" width="89.21875" style="5" customWidth="1"/>
-    <col min="7" max="7" width="17.21875" style="5" customWidth="1"/>
-    <col min="8" max="8" width="38.109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="22.77734375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="30.21875" style="5" customWidth="1"/>
-    <col min="11" max="11" width="17.88671875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="5"/>
+    <col min="2" max="2" width="23.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="22" style="6" customWidth="1"/>
+    <col min="4" max="4" width="18.21875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="26" style="6" customWidth="1"/>
+    <col min="6" max="6" width="89.21875" style="6" customWidth="1"/>
+    <col min="7" max="7" width="17.21875" style="6" customWidth="1"/>
+    <col min="8" max="8" width="38.109375" style="6" customWidth="1"/>
+    <col min="9" max="9" width="22.77734375" style="6" customWidth="1"/>
+    <col min="10" max="10" width="30.21875" style="6" customWidth="1"/>
+    <col min="11" max="11" width="17.88671875" style="6" customWidth="1"/>
     <col min="12" max="12" width="21.33203125" style="7" customWidth="1"/>
     <col min="13" max="13" width="40.6640625" style="7" customWidth="1"/>
     <col min="14" max="14" width="44.5546875" style="7" customWidth="1"/>
@@ -557,7 +561,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -574,7 +578,7 @@
       <c r="N1" s="8"/>
       <c r="O1" s="8"/>
     </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:15" s="1" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -596,7 +600,9 @@
       <c r="G2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="3"/>
+      <c r="H2" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="I2" s="4" t="s">
         <v>6</v>
       </c>
@@ -616,7 +622,7 @@
         <v>11</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
